--- a/source/bin/excel/shoot.xlsx
+++ b/source/bin/excel/shoot.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Work\Git\liqi-excel\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\liqi-excel\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2482ABD7-FDA0-4A60-9FCA-927891B36A7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2760B69-DD6F-4556-ADB3-B2CB38514131}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="885" yWindow="-120" windowWidth="28035" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="export" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="76">
   <si>
     <t>sheet</t>
   </si>
@@ -303,6 +303,14 @@
   </si>
   <si>
     <t>bullet_item_id</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>star_num</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>星星数</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2121,18 +2129,19 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA261205-B696-46A1-91EC-8341C3D2B5F8}">
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="11" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.625" customWidth="1"/>
     <col min="4" max="4" width="15.375" customWidth="1"/>
     <col min="5" max="5" width="21.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="35.75" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.875" customWidth="1"/>
+    <col min="7" max="7" width="35.75" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>17</v>
       </c>
@@ -2149,13 +2158,16 @@
         <v>68</v>
       </c>
       <c r="F1" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>18</v>
       </c>
@@ -2172,13 +2184,16 @@
         <v>69</v>
       </c>
       <c r="F2" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="H2" s="3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>20</v>
       </c>
@@ -2200,13 +2215,16 @@
       <c r="G3" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>40</v>
       </c>
@@ -2223,13 +2241,16 @@
         <v>3</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G5">
-        <v>251101</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>251101</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B6">
         <v>101101</v>
       </c>
@@ -2243,13 +2264,16 @@
         <v>3</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G6">
-        <v>251101</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+        <v>3</v>
+      </c>
+      <c r="H6">
+        <v>251101</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B7">
         <v>101101</v>
       </c>
@@ -2262,11 +2286,14 @@
       <c r="E7">
         <v>3</v>
       </c>
-      <c r="G7">
-        <v>251101</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F7">
+        <v>5</v>
+      </c>
+      <c r="H7">
+        <v>251101</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>39</v>
       </c>
@@ -2283,13 +2310,16 @@
         <v>2</v>
       </c>
       <c r="F8">
+        <v>3</v>
+      </c>
+      <c r="G8">
         <v>11</v>
       </c>
-      <c r="G8">
-        <v>251101</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H8">
+        <v>251101</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B9">
         <v>101102</v>
       </c>
@@ -2303,13 +2333,16 @@
         <v>2</v>
       </c>
       <c r="F9">
+        <v>3</v>
+      </c>
+      <c r="G9">
         <v>14</v>
       </c>
-      <c r="G9">
-        <v>251101</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H9">
+        <v>251101</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B10">
         <v>101102</v>
       </c>
@@ -2323,13 +2356,16 @@
         <v>2</v>
       </c>
       <c r="F10">
+        <v>3</v>
+      </c>
+      <c r="G10">
         <v>15</v>
       </c>
-      <c r="G10">
-        <v>251101</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H10">
+        <v>251101</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B11">
         <v>101102</v>
       </c>
@@ -2343,13 +2379,16 @@
         <v>2</v>
       </c>
       <c r="F11">
+        <v>3</v>
+      </c>
+      <c r="G11">
         <v>20</v>
       </c>
-      <c r="G11">
-        <v>251101</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H11">
+        <v>251101</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B12">
         <v>101102</v>
       </c>
@@ -2362,11 +2401,14 @@
       <c r="E12">
         <v>2</v>
       </c>
-      <c r="G12">
-        <v>251101</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F12">
+        <v>3</v>
+      </c>
+      <c r="H12">
+        <v>251101</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>41</v>
       </c>
@@ -2383,13 +2425,16 @@
         <v>1</v>
       </c>
       <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13">
         <v>22</v>
       </c>
-      <c r="G13">
-        <v>251101</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H13">
+        <v>251101</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B14">
         <v>101103</v>
       </c>
@@ -2403,13 +2448,16 @@
         <v>1</v>
       </c>
       <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14">
         <v>23</v>
       </c>
-      <c r="G14">
-        <v>251101</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H14">
+        <v>251101</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B15">
         <v>101103</v>
       </c>
@@ -2422,11 +2470,14 @@
       <c r="E15">
         <v>1</v>
       </c>
-      <c r="G15">
-        <v>251101</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="H15">
+        <v>251101</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B16">
         <v>101103</v>
       </c>
@@ -2440,13 +2491,16 @@
         <v>1</v>
       </c>
       <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16">
         <v>24</v>
       </c>
-      <c r="G16">
-        <v>251101</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H16">
+        <v>251101</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B17">
         <v>101103</v>
       </c>
@@ -2459,11 +2513,14 @@
       <c r="E17">
         <v>1</v>
       </c>
-      <c r="G17">
-        <v>251101</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="H17">
+        <v>251101</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B18">
         <v>101103</v>
       </c>
@@ -2476,11 +2533,14 @@
       <c r="E18">
         <v>1</v>
       </c>
-      <c r="G18">
-        <v>251101</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="H18">
+        <v>251101</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B19">
         <v>101103</v>
       </c>
@@ -2493,11 +2553,14 @@
       <c r="E19">
         <v>1</v>
       </c>
-      <c r="G19">
-        <v>251101</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="H19">
+        <v>251101</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>40</v>
       </c>
@@ -2514,13 +2577,16 @@
         <v>3</v>
       </c>
       <c r="F20" s="4">
-        <v>2</v>
-      </c>
-      <c r="G20">
-        <v>251101</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+      <c r="G20" s="4">
+        <v>2</v>
+      </c>
+      <c r="H20">
+        <v>251101</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B21">
         <v>101201</v>
       </c>
@@ -2533,12 +2599,15 @@
       <c r="E21" s="4">
         <v>3</v>
       </c>
-      <c r="F21" s="4"/>
-      <c r="G21">
-        <v>251101</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F21" s="4">
+        <v>5</v>
+      </c>
+      <c r="G21" s="4"/>
+      <c r="H21">
+        <v>251101</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B22">
         <v>101201</v>
       </c>
@@ -2551,12 +2620,15 @@
       <c r="E22" s="4">
         <v>3</v>
       </c>
-      <c r="F22" s="4"/>
-      <c r="G22">
-        <v>251101</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F22" s="4">
+        <v>5</v>
+      </c>
+      <c r="G22" s="4"/>
+      <c r="H22">
+        <v>251101</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>39</v>
       </c>
@@ -2573,13 +2645,16 @@
         <v>2</v>
       </c>
       <c r="F23" s="4">
+        <v>3</v>
+      </c>
+      <c r="G23" s="4">
         <v>13</v>
       </c>
-      <c r="G23">
-        <v>251101</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H23">
+        <v>251101</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B24">
         <v>101202</v>
       </c>
@@ -2593,13 +2668,16 @@
         <v>2</v>
       </c>
       <c r="F24" s="4">
+        <v>3</v>
+      </c>
+      <c r="G24" s="4">
         <v>16</v>
       </c>
-      <c r="G24">
-        <v>251101</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H24">
+        <v>251101</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B25">
         <v>101202</v>
       </c>
@@ -2613,13 +2691,16 @@
         <v>2</v>
       </c>
       <c r="F25" s="4">
+        <v>3</v>
+      </c>
+      <c r="G25" s="4">
         <v>18</v>
       </c>
-      <c r="G25">
-        <v>251101</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H25">
+        <v>251101</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B26">
         <v>101202</v>
       </c>
@@ -2632,12 +2713,15 @@
       <c r="E26" s="4">
         <v>2</v>
       </c>
-      <c r="F26" s="4"/>
-      <c r="G26">
-        <v>251101</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F26" s="4">
+        <v>3</v>
+      </c>
+      <c r="G26" s="4"/>
+      <c r="H26">
+        <v>251101</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B27">
         <v>101202</v>
       </c>
@@ -2650,12 +2734,15 @@
       <c r="E27" s="4">
         <v>2</v>
       </c>
-      <c r="F27" s="4"/>
-      <c r="G27">
-        <v>251101</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F27" s="4">
+        <v>3</v>
+      </c>
+      <c r="G27" s="4"/>
+      <c r="H27">
+        <v>251101</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>41</v>
       </c>
@@ -2671,12 +2758,15 @@
       <c r="E28" s="4">
         <v>1</v>
       </c>
-      <c r="F28" s="4"/>
-      <c r="G28">
-        <v>251101</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F28" s="4">
+        <v>1</v>
+      </c>
+      <c r="G28" s="4"/>
+      <c r="H28">
+        <v>251101</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B29">
         <v>101203</v>
       </c>
@@ -2689,12 +2779,15 @@
       <c r="E29" s="4">
         <v>1</v>
       </c>
-      <c r="F29" s="4"/>
-      <c r="G29">
-        <v>251101</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F29" s="4">
+        <v>1</v>
+      </c>
+      <c r="G29" s="4"/>
+      <c r="H29">
+        <v>251101</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B30">
         <v>101203</v>
       </c>
@@ -2707,12 +2800,15 @@
       <c r="E30" s="4">
         <v>1</v>
       </c>
-      <c r="F30" s="4"/>
-      <c r="G30">
-        <v>251101</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F30" s="4">
+        <v>1</v>
+      </c>
+      <c r="G30" s="4"/>
+      <c r="H30">
+        <v>251101</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B31">
         <v>101203</v>
       </c>
@@ -2725,12 +2821,15 @@
       <c r="E31" s="4">
         <v>1</v>
       </c>
-      <c r="F31" s="4"/>
-      <c r="G31">
-        <v>251101</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F31" s="4">
+        <v>1</v>
+      </c>
+      <c r="G31" s="4"/>
+      <c r="H31">
+        <v>251101</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B32">
         <v>101203</v>
       </c>
@@ -2743,12 +2842,15 @@
       <c r="E32" s="4">
         <v>1</v>
       </c>
-      <c r="F32" s="4"/>
-      <c r="G32">
-        <v>251101</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F32" s="4">
+        <v>1</v>
+      </c>
+      <c r="G32" s="4"/>
+      <c r="H32">
+        <v>251101</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B33">
         <v>101203</v>
       </c>
@@ -2761,12 +2863,15 @@
       <c r="E33" s="4">
         <v>1</v>
       </c>
-      <c r="F33" s="4"/>
-      <c r="G33">
-        <v>251101</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F33" s="4">
+        <v>1</v>
+      </c>
+      <c r="G33" s="4"/>
+      <c r="H33">
+        <v>251101</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B34">
         <v>101203</v>
       </c>
@@ -2779,12 +2884,15 @@
       <c r="E34" s="4">
         <v>1</v>
       </c>
-      <c r="F34" s="4"/>
-      <c r="G34">
-        <v>251101</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F34" s="4">
+        <v>1</v>
+      </c>
+      <c r="G34" s="4"/>
+      <c r="H34">
+        <v>251101</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>40</v>
       </c>
@@ -2800,11 +2908,14 @@
       <c r="E35">
         <v>3</v>
       </c>
-      <c r="G35">
-        <v>251101</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F35">
+        <v>5</v>
+      </c>
+      <c r="H35">
+        <v>251101</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B36">
         <v>101301</v>
       </c>
@@ -2817,11 +2928,14 @@
       <c r="E36">
         <v>3</v>
       </c>
-      <c r="G36">
-        <v>251101</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F36">
+        <v>5</v>
+      </c>
+      <c r="H36">
+        <v>251101</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B37">
         <v>101301</v>
       </c>
@@ -2834,11 +2948,14 @@
       <c r="E37">
         <v>3</v>
       </c>
-      <c r="G37">
-        <v>251101</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F37">
+        <v>5</v>
+      </c>
+      <c r="H37">
+        <v>251101</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
         <v>39</v>
       </c>
@@ -2855,13 +2972,16 @@
         <v>2</v>
       </c>
       <c r="F38">
+        <v>3</v>
+      </c>
+      <c r="G38">
         <v>12</v>
       </c>
-      <c r="G38">
-        <v>251101</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H38">
+        <v>251101</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B39">
         <v>101302</v>
       </c>
@@ -2875,13 +2995,16 @@
         <v>2</v>
       </c>
       <c r="F39">
+        <v>3</v>
+      </c>
+      <c r="G39">
         <v>17</v>
       </c>
-      <c r="G39">
-        <v>251101</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H39">
+        <v>251101</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B40">
         <v>101302</v>
       </c>
@@ -2895,13 +3018,16 @@
         <v>2</v>
       </c>
       <c r="F40">
+        <v>3</v>
+      </c>
+      <c r="G40">
         <v>19</v>
       </c>
-      <c r="G40">
-        <v>251101</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H40">
+        <v>251101</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B41">
         <v>101302</v>
       </c>
@@ -2914,11 +3040,14 @@
       <c r="E41">
         <v>2</v>
       </c>
-      <c r="G41">
-        <v>251101</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F41">
+        <v>3</v>
+      </c>
+      <c r="H41">
+        <v>251101</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B42">
         <v>101302</v>
       </c>
@@ -2931,11 +3060,14 @@
       <c r="E42">
         <v>2</v>
       </c>
-      <c r="G42">
-        <v>251101</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F42">
+        <v>3</v>
+      </c>
+      <c r="H42">
+        <v>251101</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>41</v>
       </c>
@@ -2951,11 +3083,14 @@
       <c r="E43">
         <v>1</v>
       </c>
-      <c r="G43">
-        <v>251101</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F43">
+        <v>1</v>
+      </c>
+      <c r="H43">
+        <v>251101</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B44">
         <v>101303</v>
       </c>
@@ -2968,11 +3103,14 @@
       <c r="E44">
         <v>1</v>
       </c>
-      <c r="G44">
-        <v>251101</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F44">
+        <v>1</v>
+      </c>
+      <c r="H44">
+        <v>251101</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B45">
         <v>101303</v>
       </c>
@@ -2985,11 +3123,14 @@
       <c r="E45">
         <v>1</v>
       </c>
-      <c r="G45">
-        <v>251101</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F45">
+        <v>1</v>
+      </c>
+      <c r="H45">
+        <v>251101</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B46">
         <v>101303</v>
       </c>
@@ -3002,11 +3143,14 @@
       <c r="E46">
         <v>1</v>
       </c>
-      <c r="G46">
-        <v>251101</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F46">
+        <v>1</v>
+      </c>
+      <c r="H46">
+        <v>251101</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B47">
         <v>101303</v>
       </c>
@@ -3019,11 +3163,14 @@
       <c r="E47">
         <v>1</v>
       </c>
-      <c r="G47">
-        <v>251101</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F47">
+        <v>1</v>
+      </c>
+      <c r="H47">
+        <v>251101</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B48">
         <v>101303</v>
       </c>
@@ -3036,11 +3183,14 @@
       <c r="E48">
         <v>1</v>
       </c>
-      <c r="G48">
-        <v>251101</v>
-      </c>
-    </row>
-    <row r="49" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="F48">
+        <v>1</v>
+      </c>
+      <c r="H48">
+        <v>251101</v>
+      </c>
+    </row>
+    <row r="49" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B49">
         <v>101303</v>
       </c>
@@ -3053,7 +3203,10 @@
       <c r="E49">
         <v>1</v>
       </c>
-      <c r="G49">
+      <c r="F49">
+        <v>1</v>
+      </c>
+      <c r="H49">
         <v>251101</v>
       </c>
     </row>
